--- a/data/trans_orig/IP16A08-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Clase-trans_orig.xlsx
@@ -733,47 +733,47 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5340</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>658</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5190</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1439</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>15610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20808</t>
+          <t>20804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28414</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>9697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34978</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11307</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18128</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>20374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>28486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,16%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>30446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36764</t>
+          <t>36408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35960</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>61579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70846</t>
+          <t>70911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11636</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17561</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34175</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10061</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8128</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>15222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23990</t>
+          <t>24139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29475</t>
+          <t>29191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>30049</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48523</t>
+          <t>48606</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85744</t>
+          <t>85595</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98441</t>
+          <t>98051</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>105822</t>
+          <t>106106</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>120404</t>
+          <t>120036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>196507</t>
+          <t>196424</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>215398</t>
+          <t>214981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20243</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34676</t>
+          <t>34971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41058</t>
+          <t>40974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8501</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>30086</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>34521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>9339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12408</t>
+          <t>11783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15942</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24498</t>
+          <t>24874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36235</t>
+          <t>36860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>42867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53052</t>
+          <t>52921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83054</t>
+          <t>82678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96052</t>
+          <t>95508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>88,8%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2447</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18542</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>26198</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20638</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41701</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51108</t>
+          <t>51100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23737</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>12116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>26369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44975</t>
+          <t>44464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>115421</t>
+          <t>115310</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128490</t>
+          <t>128459</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>121836</t>
+          <t>121274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134797</t>
+          <t>134563</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>240861</t>
+          <t>241372</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>259955</t>
+          <t>259467</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7621</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>21652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29469</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14684</t>
+          <t>14722</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>25912</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8624</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>19835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37865</t>
+          <t>37581</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44516</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20407</t>
+          <t>20474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>29370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>61509</t>
+          <t>61178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>72523</t>
+          <t>72342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>17554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41993</t>
+          <t>42222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>50087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8335</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>12433</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>24791</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>24215</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25797</t>
+          <t>25895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43998</t>
+          <t>44465</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97095</t>
+          <t>98029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>110926</t>
+          <t>111099</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93078</t>
+          <t>92820</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106130</t>
+          <t>105805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>195857</t>
+          <t>195390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>214058</t>
+          <t>213960</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8247</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16605</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23369</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>26482</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46086</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53725</t>
+          <t>53986</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>18166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22368</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>35001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44430</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13011</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>929</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>12429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66449</t>
+          <t>66637</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75964</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49640</t>
+          <t>49635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54833</t>
+          <t>54915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>119392</t>
+          <t>119796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129426</t>
+          <t>129877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15465</t>
+          <t>15801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21148</t>
+          <t>21302</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27698</t>
+          <t>27577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24865</t>
+          <t>23793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33108</t>
+          <t>32798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49418</t>
+          <t>49082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59912</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26670</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12078</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>46157</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151854</t>
+          <t>151539</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>167057</t>
+          <t>167174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>151432</t>
+          <t>152176</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>167231</t>
+          <t>167297</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>309234</t>
+          <t>308540</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>330427</t>
+          <t>331331</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
